--- a/data/trans_orig/P6702-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6702-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la distribución de tareas es irregular y provoca que se le acumule el trabajo en 2012</t>
+          <t>Población según si la distribución de tareas es irregular y provoca que se le acumule el trabajo en 2012 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23278</t>
+          <t>22621</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43926</t>
+          <t>42869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37990</t>
+          <t>37382</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61922</t>
+          <t>61280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65441</t>
+          <t>64328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97070</t>
+          <t>97210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20360</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40765</t>
+          <t>41378</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>17537</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35301</t>
+          <t>35180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43277</t>
+          <t>41870</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69181</t>
+          <t>69424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55202</t>
+          <t>54432</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80766</t>
+          <t>80241</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30323</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51156</t>
+          <t>51545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>89975</t>
+          <t>91164</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>124473</t>
+          <t>125702</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25100</t>
+          <t>26357</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47844</t>
+          <t>48870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22317</t>
+          <t>21333</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37025</t>
+          <t>37225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63311</t>
+          <t>64303</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29579</t>
+          <t>29597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20664</t>
+          <t>22347</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44403</t>
+          <t>44962</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142188</t>
+          <t>142798</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191131</t>
+          <t>191269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89028</t>
+          <t>88446</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125962</t>
+          <t>127483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>246288</t>
+          <t>243662</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304538</t>
+          <t>307817</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114009</t>
+          <t>113185</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>159364</t>
+          <t>161102</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76513</t>
+          <t>79150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113007</t>
+          <t>114508</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>201663</t>
+          <t>201358</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262605</t>
+          <t>262145</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>272075</t>
+          <t>273413</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>331867</t>
+          <t>332262</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>170520</t>
+          <t>168358</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>215112</t>
+          <t>212402</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>457791</t>
+          <t>459736</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>533380</t>
+          <t>530649</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>165964</t>
+          <t>165474</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215894</t>
+          <t>216893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95007</t>
+          <t>97614</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>135200</t>
+          <t>135723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>274305</t>
+          <t>273635</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>337909</t>
+          <t>337607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101323</t>
+          <t>99538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144435</t>
+          <t>142553</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48580</t>
+          <t>48110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77580</t>
+          <t>77874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157751</t>
+          <t>157390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>208854</t>
+          <t>210799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34331</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61489</t>
+          <t>65194</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41260</t>
+          <t>41095</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68099</t>
+          <t>69101</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84908</t>
+          <t>84037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121176</t>
+          <t>121161</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35219</t>
+          <t>36474</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63981</t>
+          <t>64230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>20839</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42515</t>
+          <t>42059</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62012</t>
+          <t>61226</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>96178</t>
+          <t>98657</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97043</t>
+          <t>96879</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133921</t>
+          <t>135825</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>64995</t>
+          <t>64545</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95939</t>
+          <t>96229</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>169358</t>
+          <t>170057</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>216702</t>
+          <t>218963</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51925</t>
+          <t>51753</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81710</t>
+          <t>81262</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29551</t>
+          <t>30383</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55531</t>
+          <t>55442</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89053</t>
+          <t>87251</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127955</t>
+          <t>127281</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27627</t>
+          <t>27206</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53295</t>
+          <t>54215</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20670</t>
+          <t>19868</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41834</t>
+          <t>41579</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54516</t>
+          <t>53311</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87432</t>
+          <t>87389</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>220489</t>
+          <t>218881</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>278586</t>
+          <t>278373</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185641</t>
+          <t>182307</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>237352</t>
+          <t>237343</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>420265</t>
+          <t>421670</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>496442</t>
+          <t>503205</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>186665</t>
+          <t>186747</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242515</t>
+          <t>241312</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128093</t>
+          <t>128186</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>174063</t>
+          <t>175062</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>329369</t>
+          <t>328155</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>397625</t>
+          <t>400034</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>448755</t>
+          <t>449259</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>525177</t>
+          <t>522291</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>278307</t>
+          <t>281804</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>339390</t>
+          <t>340582</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>748089</t>
+          <t>744418</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>838316</t>
+          <t>838449</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>261490</t>
+          <t>262298</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>326655</t>
+          <t>322999</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>147682</t>
+          <t>146677</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>197651</t>
+          <t>196984</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>423554</t>
+          <t>423836</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>501998</t>
+          <t>500501</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>152905</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>206739</t>
+          <t>206436</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>85062</t>
+          <t>85163</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>126147</t>
+          <t>125907</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>249327</t>
+          <t>249189</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>316595</t>
+          <t>315404</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la distribución de tareas es irregular y provoca que se le acumule el trabajo en 2016</t>
+          <t>Población según si la distribución de tareas es irregular y provoca que se le acumule el trabajo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37935</t>
+          <t>38359</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24533</t>
+          <t>24541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32488</t>
+          <t>32845</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56836</t>
+          <t>56663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29013</t>
+          <t>28429</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16778</t>
+          <t>18953</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19065</t>
+          <t>19034</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40232</t>
+          <t>39994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38563</t>
+          <t>39146</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61971</t>
+          <t>62073</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34038</t>
+          <t>34868</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63827</t>
+          <t>63707</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91808</t>
+          <t>90951</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20904</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40201</t>
+          <t>41614</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19892</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31358</t>
+          <t>31890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54825</t>
+          <t>55881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,97%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25485</t>
+          <t>27524</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>15434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>33427</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129284</t>
+          <t>128968</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179450</t>
+          <t>175559</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100983</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141087</t>
+          <t>138511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>242018</t>
+          <t>239101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>301926</t>
+          <t>301435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134354</t>
+          <t>134540</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>182277</t>
+          <t>180871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90674</t>
+          <t>90299</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129518</t>
+          <t>127546</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>235525</t>
+          <t>234046</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>296650</t>
+          <t>294041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>271951</t>
+          <t>275932</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>332925</t>
+          <t>333136</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>195566</t>
+          <t>194821</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>242966</t>
+          <t>244287</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>487162</t>
+          <t>484738</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>562667</t>
+          <t>563104</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186283</t>
+          <t>188475</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>239566</t>
+          <t>240209</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124266</t>
+          <t>124118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167646</t>
+          <t>166831</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>324450</t>
+          <t>323153</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>391855</t>
+          <t>391913</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83004</t>
+          <t>84270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124136</t>
+          <t>125816</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45634</t>
+          <t>46682</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75544</t>
+          <t>76587</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137115</t>
+          <t>137187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>186568</t>
+          <t>187597</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42325</t>
+          <t>42229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70599</t>
+          <t>69013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54019</t>
+          <t>54142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82834</t>
+          <t>83220</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103360</t>
+          <t>104007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>146139</t>
+          <t>144314</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64986</t>
+          <t>64187</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98891</t>
+          <t>97858</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40953</t>
+          <t>41045</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67624</t>
+          <t>66517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>113421</t>
+          <t>112206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>157835</t>
+          <t>153086</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>104593</t>
+          <t>104645</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>142915</t>
+          <t>140830</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83049</t>
+          <t>84057</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>114353</t>
+          <t>115599</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>197190</t>
+          <t>196647</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>247016</t>
+          <t>245432</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49530</t>
+          <t>49617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81518</t>
+          <t>79790</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45307</t>
+          <t>45378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72435</t>
+          <t>71800</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103234</t>
+          <t>97307</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144005</t>
+          <t>141755</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>18877</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39927</t>
+          <t>39424</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21662</t>
+          <t>22254</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43131</t>
+          <t>42966</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45621</t>
+          <t>46079</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75188</t>
+          <t>75136</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>203221</t>
+          <t>202806</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>261297</t>
+          <t>261158</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>177952</t>
+          <t>176756</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>230936</t>
+          <t>230387</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>400136</t>
+          <t>396271</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>476881</t>
+          <t>474456</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229370</t>
+          <t>226864</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>289632</t>
+          <t>287763</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>150687</t>
+          <t>149324</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>198159</t>
+          <t>196227</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>393994</t>
+          <t>391700</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>467668</t>
+          <t>468062</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>438684</t>
+          <t>438794</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>513506</t>
+          <t>508427</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>318021</t>
+          <t>315303</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>375168</t>
+          <t>374351</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>772026</t>
+          <t>777626</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>862852</t>
+          <t>868747</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>273606</t>
+          <t>276255</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>339030</t>
+          <t>338921</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>190444</t>
+          <t>191939</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>241067</t>
+          <t>242642</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>483796</t>
+          <t>484168</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>565410</t>
+          <t>564700</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>122920</t>
+          <t>124447</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>171255</t>
+          <t>173993</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>79309</t>
+          <t>79109</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>116733</t>
+          <t>115351</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>212543</t>
+          <t>215564</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>275864</t>
+          <t>275765</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la distribución de tareas es irregular y provoca que se le acumule el trabajo en 2023</t>
+          <t>Población según si la distribución de tareas es irregular y provoca que se le acumule el trabajo en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20495</t>
+          <t>20866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>12916</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20563</t>
+          <t>20652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8007</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26791</t>
+          <t>27060</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>6991</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15699</t>
+          <t>15306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6453</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84212</t>
+          <t>86213</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>436096</t>
+          <t>449787</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40611</t>
+          <t>40683</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62645</t>
+          <t>63100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141436</t>
+          <t>137699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>573396</t>
+          <t>569198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14114</t>
+          <t>12311</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101616</t>
+          <t>102584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>20793</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38211</t>
+          <t>38010</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31645</t>
+          <t>30153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125730</t>
+          <t>124581</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27383</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>190930</t>
+          <t>194431</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62275</t>
+          <t>60763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86647</t>
+          <t>84486</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>72964</t>
+          <t>69752</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>258903</t>
+          <t>261804</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17281</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117884</t>
+          <t>117274</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>42048</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67131</t>
+          <t>66072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47808</t>
+          <t>47527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175168</t>
+          <t>175492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44295</t>
+          <t>44266</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14549</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30932</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15462</t>
+          <t>14746</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70696</t>
+          <t>68707</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45563</t>
+          <t>45695</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69822</t>
+          <t>69925</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29288</t>
+          <t>29721</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48190</t>
+          <t>47674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81321</t>
+          <t>82126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111138</t>
+          <t>111862</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,44%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>26144</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19785</t>
+          <t>19505</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39966</t>
+          <t>40312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>22174</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44027</t>
+          <t>43801</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24721</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41760</t>
+          <t>42325</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52675</t>
+          <t>53079</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78614</t>
+          <t>81242</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17212</t>
+          <t>17045</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42790</t>
+          <t>42023</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>12708</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17534</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>171791</t>
+          <t>172897</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>553302</t>
+          <t>539351</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80096</t>
+          <t>79959</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>109764</t>
+          <t>107779</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>264183</t>
+          <t>268523</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>724943</t>
+          <t>753139</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22538</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>108528</t>
+          <t>109608</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40536</t>
+          <t>41192</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63216</t>
+          <t>62646</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52125</t>
+          <t>51869</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>158845</t>
+          <t>157019</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52890</t>
+          <t>58245</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>231304</t>
+          <t>232355</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>98816</t>
+          <t>96402</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>125042</t>
+          <t>126062</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>130077</t>
+          <t>120923</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>344766</t>
+          <t>338809</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>28383</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136546</t>
+          <t>134756</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56973</t>
+          <t>55370</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>84183</t>
+          <t>82827</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77774</t>
+          <t>69794</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>205033</t>
+          <t>205848</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>45958</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20580</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40232</t>
+          <t>39002</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24743</t>
+          <t>24214</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>77386</t>
+          <t>77255</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6702-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6702-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>22294</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42869</t>
+          <t>43300</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37382</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61280</t>
+          <t>60717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64328</t>
+          <t>65926</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97210</t>
+          <t>97561</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20111</t>
+          <t>20857</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>40534</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>17461</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35180</t>
+          <t>36571</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41870</t>
+          <t>41895</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69424</t>
+          <t>70041</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54432</t>
+          <t>53949</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80241</t>
+          <t>79503</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29164</t>
+          <t>29156</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51545</t>
+          <t>50381</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91164</t>
+          <t>90105</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>125702</t>
+          <t>124282</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26357</t>
+          <t>26940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48870</t>
+          <t>49229</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37225</t>
+          <t>38191</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64303</t>
+          <t>64745</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29597</t>
+          <t>30138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22347</t>
+          <t>21021</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22184</t>
+          <t>21692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44962</t>
+          <t>43942</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142798</t>
+          <t>143349</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191269</t>
+          <t>193987</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88446</t>
+          <t>89683</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127483</t>
+          <t>128166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243662</t>
+          <t>245913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>307817</t>
+          <t>309700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113185</t>
+          <t>114382</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161102</t>
+          <t>160939</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79150</t>
+          <t>77377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114508</t>
+          <t>114424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>201358</t>
+          <t>201019</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262145</t>
+          <t>260338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>273413</t>
+          <t>271734</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>332262</t>
+          <t>329695</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>168358</t>
+          <t>169242</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212402</t>
+          <t>216231</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>459736</t>
+          <t>456589</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>530649</t>
+          <t>531330</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>165474</t>
+          <t>165441</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>216893</t>
+          <t>216056</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97614</t>
+          <t>98255</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>135723</t>
+          <t>137195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>273635</t>
+          <t>275452</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>337607</t>
+          <t>340674</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99538</t>
+          <t>99653</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142553</t>
+          <t>142110</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48110</t>
+          <t>47377</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77874</t>
+          <t>78676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157390</t>
+          <t>153996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>210799</t>
+          <t>208148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35859</t>
+          <t>35122</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65194</t>
+          <t>61215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41095</t>
+          <t>42359</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69101</t>
+          <t>69633</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84037</t>
+          <t>82542</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121161</t>
+          <t>122042</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36474</t>
+          <t>35609</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64230</t>
+          <t>62778</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20839</t>
+          <t>20290</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42059</t>
+          <t>41521</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61226</t>
+          <t>63341</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98657</t>
+          <t>98622</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96879</t>
+          <t>97032</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135825</t>
+          <t>134840</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>64545</t>
+          <t>64008</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>96229</t>
+          <t>94528</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>170057</t>
+          <t>170395</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>218963</t>
+          <t>218325</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51753</t>
+          <t>52611</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81262</t>
+          <t>83799</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30383</t>
+          <t>28987</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55442</t>
+          <t>54802</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87251</t>
+          <t>87092</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127281</t>
+          <t>129146</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27206</t>
+          <t>27859</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54215</t>
+          <t>55279</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19868</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41579</t>
+          <t>42668</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53311</t>
+          <t>53072</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87389</t>
+          <t>88619</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>218881</t>
+          <t>220101</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>278373</t>
+          <t>278108</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>182307</t>
+          <t>183610</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>237343</t>
+          <t>241213</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>421670</t>
+          <t>415973</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>503205</t>
+          <t>499849</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>186747</t>
+          <t>184418</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241312</t>
+          <t>243490</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128186</t>
+          <t>128642</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>175062</t>
+          <t>174867</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>328155</t>
+          <t>330667</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>400034</t>
+          <t>401879</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>449259</t>
+          <t>448250</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>522291</t>
+          <t>523284</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>281804</t>
+          <t>279022</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>340582</t>
+          <t>337607</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>744418</t>
+          <t>743131</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>838449</t>
+          <t>837233</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>262298</t>
+          <t>261672</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>322999</t>
+          <t>326333</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>146677</t>
+          <t>145169</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>196984</t>
+          <t>195583</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>423836</t>
+          <t>423993</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>500501</t>
+          <t>503265</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>153667</t>
+          <t>152987</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>206436</t>
+          <t>204781</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>85163</t>
+          <t>84201</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>125907</t>
+          <t>125084</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>249189</t>
+          <t>248587</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>315404</t>
+          <t>317059</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>18128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38359</t>
+          <t>37900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10265</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24541</t>
+          <t>24098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32845</t>
+          <t>32963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56663</t>
+          <t>57074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>11282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28429</t>
+          <t>27692</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19034</t>
+          <t>18883</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39994</t>
+          <t>39648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39146</t>
+          <t>39450</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62073</t>
+          <t>63323</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18675</t>
+          <t>19067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34868</t>
+          <t>35315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63707</t>
+          <t>63423</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90951</t>
+          <t>90249</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>41,94%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21386</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41614</t>
+          <t>40330</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7701</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31890</t>
+          <t>31208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55881</t>
+          <t>55966</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27524</t>
+          <t>27122</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12578</t>
+          <t>12263</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33427</t>
+          <t>34046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128968</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>175559</t>
+          <t>175361</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,82 +4388,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>18,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>119141</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>98468</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>140882</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>18,25%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>21,58%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>269803</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>239401</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>299532</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>17,1%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>15,17%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>18,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>119141</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>99955</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>138511</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,25%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>15,31%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>21,22%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>269803</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>239101</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>301435</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>17,1%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>15,15%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134540</t>
+          <t>133945</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180871</t>
+          <t>182141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90299</t>
+          <t>91708</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127546</t>
+          <t>131295</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>234046</t>
+          <t>238697</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>294041</t>
+          <t>296909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>275932</t>
+          <t>275456</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>333136</t>
+          <t>332900</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>194821</t>
+          <t>195777</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>244287</t>
+          <t>245025</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>484738</t>
+          <t>487674</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>563104</t>
+          <t>558570</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>188475</t>
+          <t>187215</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>240209</t>
+          <t>238537</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124118</t>
+          <t>123448</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>166831</t>
+          <t>165870</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>323153</t>
+          <t>322943</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>391913</t>
+          <t>394873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84270</t>
+          <t>83132</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125816</t>
+          <t>123560</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46682</t>
+          <t>46034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76587</t>
+          <t>74454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137187</t>
+          <t>135921</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>187597</t>
+          <t>184782</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42229</t>
+          <t>41744</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69013</t>
+          <t>71047</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54142</t>
+          <t>53099</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83220</t>
+          <t>84509</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104007</t>
+          <t>103574</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>144314</t>
+          <t>146543</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64187</t>
+          <t>63642</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97858</t>
+          <t>97473</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41045</t>
+          <t>41748</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66517</t>
+          <t>68193</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>112206</t>
+          <t>114465</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153086</t>
+          <t>154923</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>104645</t>
+          <t>105099</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>140830</t>
+          <t>142132</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84057</t>
+          <t>83188</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>115599</t>
+          <t>114560</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>196647</t>
+          <t>198936</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>245432</t>
+          <t>248861</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>48117</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79790</t>
+          <t>78924</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45378</t>
+          <t>44264</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71800</t>
+          <t>72241</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>97307</t>
+          <t>102298</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>141755</t>
+          <t>141845</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>19174</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39424</t>
+          <t>40458</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22254</t>
+          <t>21569</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42966</t>
+          <t>43498</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46079</t>
+          <t>46524</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75136</t>
+          <t>75687</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>202806</t>
+          <t>206060</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>261158</t>
+          <t>265081</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>176756</t>
+          <t>180120</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>230387</t>
+          <t>230170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>396271</t>
+          <t>398545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>474456</t>
+          <t>474616</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>226864</t>
+          <t>225011</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>287763</t>
+          <t>284604</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>149324</t>
+          <t>148817</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>196227</t>
+          <t>200160</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>391700</t>
+          <t>390682</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>468062</t>
+          <t>468567</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>438794</t>
+          <t>439111</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>508427</t>
+          <t>512540</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>315303</t>
+          <t>316311</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>374351</t>
+          <t>376605</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>777626</t>
+          <t>774042</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>868747</t>
+          <t>869452</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>276255</t>
+          <t>275862</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>338921</t>
+          <t>342787</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>191939</t>
+          <t>190237</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>242642</t>
+          <t>242761</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>484168</t>
+          <t>484838</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>564700</t>
+          <t>567799</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>124447</t>
+          <t>125464</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>173993</t>
+          <t>171166</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>79109</t>
+          <t>78445</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>115351</t>
+          <t>116330</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>215564</t>
+          <t>216777</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>275765</t>
+          <t>274486</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -6645,32 +6645,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>11069</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>18579</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6680,32 +6680,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6715,32 +6715,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>15184</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>22839</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -6758,32 +6758,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>13859</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>11465</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>19822</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -6871,32 +6871,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13790</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20652</t>
+          <t>26243</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6906,32 +6906,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>18546</t>
+          <t>24442</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>16043</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27060</t>
+          <t>34502</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -6984,32 +6984,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10672</t>
+          <t>14374</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7019,32 +7019,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7054,32 +7054,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>11319</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>18277</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -7132,32 +7132,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7167,32 +7167,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -7210,17 +7210,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7327,32 +7327,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>293465</t>
+          <t>54242</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86213</t>
+          <t>42566</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>449787</t>
+          <t>70463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7362,32 +7362,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51437</t>
+          <t>59020</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40683</t>
+          <t>47150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63100</t>
+          <t>72746</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7397,32 +7397,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>344901</t>
+          <t>113262</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137699</t>
+          <t>94978</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>569198</t>
+          <t>132471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -7440,32 +7440,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48533</t>
+          <t>49181</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12311</t>
+          <t>37099</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102584</t>
+          <t>66068</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7475,32 +7475,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28836</t>
+          <t>31141</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20793</t>
+          <t>23237</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38010</t>
+          <t>42386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7510,32 +7510,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>77368</t>
+          <t>80322</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>63408</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124581</t>
+          <t>98783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -7553,32 +7553,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94256</t>
+          <t>105892</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>86956</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>194431</t>
+          <t>124830</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7588,32 +7588,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73356</t>
+          <t>78321</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60763</t>
+          <t>65377</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84486</t>
+          <t>91624</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7623,32 +7623,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>167612</t>
+          <t>184213</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69752</t>
+          <t>161578</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>261804</t>
+          <t>207569</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -7666,32 +7666,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56132</t>
+          <t>64132</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14775</t>
+          <t>49690</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117274</t>
+          <t>80465</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7701,32 +7701,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53949</t>
+          <t>61463</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42048</t>
+          <t>49064</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66072</t>
+          <t>74986</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7736,32 +7736,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>110081</t>
+          <t>125595</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47527</t>
+          <t>105335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175492</t>
+          <t>145985</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -7779,32 +7779,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19419</t>
+          <t>23955</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44266</t>
+          <t>40027</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7814,32 +7814,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21629</t>
+          <t>24932</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14240</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31361</t>
+          <t>35722</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7849,32 +7849,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>41048</t>
+          <t>48888</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>36212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68707</t>
+          <t>69326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -7892,17 +7892,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7927,17 +7927,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>229206</t>
+          <t>254877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>229206</t>
+          <t>254877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>229206</t>
+          <t>254877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7962,17 +7962,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>741010</t>
+          <t>552280</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>741010</t>
+          <t>552280</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>741010</t>
+          <t>552280</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8009,32 +8009,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>57247</t>
+          <t>65830</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45695</t>
+          <t>52180</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69925</t>
+          <t>81080</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8044,32 +8044,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38969</t>
+          <t>41565</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29721</t>
+          <t>32493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47674</t>
+          <t>51516</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8079,32 +8079,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>96216</t>
+          <t>107394</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82126</t>
+          <t>91433</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111862</t>
+          <t>125477</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -8122,32 +8122,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10540</t>
+          <t>13436</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>25212</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8157,32 +8157,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18123</t>
+          <t>18782</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26144</t>
+          <t>27380</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8192,32 +8192,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>28663</t>
+          <t>32218</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19505</t>
+          <t>23213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40312</t>
+          <t>45418</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -8235,32 +8235,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32585</t>
+          <t>34211</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43801</t>
+          <t>46828</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8270,32 +8270,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>32864</t>
+          <t>36711</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25161</t>
+          <t>27446</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42325</t>
+          <t>46482</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8305,32 +8305,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>70923</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53079</t>
+          <t>58114</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>81242</t>
+          <t>86980</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -8348,32 +8348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19811</t>
+          <t>21119</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30182</t>
+          <t>31525</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8383,32 +8383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8418,32 +8418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>30637</t>
+          <t>33717</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>23066</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42023</t>
+          <t>45691</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -8461,32 +8461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8496,32 +8496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12708</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8531,32 +8531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17313</t>
+          <t>19637</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -8574,17 +8574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8609,17 +8609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8691,32 +8691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>360810</t>
+          <t>131141</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172897</t>
+          <t>109271</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>539351</t>
+          <t>153427</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8726,32 +8726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>93867</t>
+          <t>104699</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79959</t>
+          <t>89759</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107779</t>
+          <t>122192</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8761,32 +8761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>454678</t>
+          <t>235841</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>268523</t>
+          <t>208574</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>753139</t>
+          <t>261986</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -8804,32 +8804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>62889</t>
+          <t>68584</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>52869</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109608</t>
+          <t>90190</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8839,32 +8839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>50695</t>
+          <t>55421</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>41192</t>
+          <t>44099</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>62646</t>
+          <t>67784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8874,32 +8874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>113585</t>
+          <t>124005</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51869</t>
+          <t>103525</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>157019</t>
+          <t>148990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -8917,32 +8917,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140631</t>
+          <t>157386</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58245</t>
+          <t>133291</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>232355</t>
+          <t>181090</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8952,32 +8952,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>110975</t>
+          <t>122192</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>96402</t>
+          <t>105494</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>126062</t>
+          <t>138158</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8987,32 +8987,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>251606</t>
+          <t>279578</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>120923</t>
+          <t>250631</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>338809</t>
+          <t>309867</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -9030,32 +9030,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>81179</t>
+          <t>92361</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28383</t>
+          <t>74491</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>134756</t>
+          <t>113782</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9065,32 +9065,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>68568</t>
+          <t>78270</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55370</t>
+          <t>65228</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82827</t>
+          <t>92298</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9100,32 +9100,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>149747</t>
+          <t>170631</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69794</t>
+          <t>149168</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>205848</t>
+          <t>196007</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -9143,32 +9143,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>24451</t>
+          <t>29301</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45958</t>
+          <t>47396</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9178,32 +9178,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>33120</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19364</t>
+          <t>23260</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39002</t>
+          <t>45047</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9213,32 +9213,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>53455</t>
+          <t>62420</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>47298</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>77255</t>
+          <t>82577</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -9256,17 +9256,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9291,17 +9291,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>353110</t>
+          <t>393702</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>353110</t>
+          <t>393702</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>353110</t>
+          <t>393702</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9326,17 +9326,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1023071</t>
+          <t>872475</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1023071</t>
+          <t>872475</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1023071</t>
+          <t>872475</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
